--- a/Team-Data/2008-09/3-10-2008-09.xlsx
+++ b/Team-Data/2008-09/3-10-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -769,13 +836,13 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
         <v>29</v>
@@ -796,13 +863,13 @@
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -843,88 +910,88 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.762</v>
+        <v>0.766</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.487</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P3" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,19 +1018,19 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>5</v>
@@ -975,13 +1042,13 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,7 +1110,7 @@
         <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.454</v>
@@ -1055,7 +1122,7 @@
         <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="O4" t="n">
         <v>17.8</v>
@@ -1064,22 +1131,22 @@
         <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
         <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U4" t="n">
         <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1088,31 +1155,31 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="n">
         <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>3</v>
@@ -1133,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1145,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1157,10 +1224,10 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.453</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,28 +1292,28 @@
         <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
         <v>12.2</v>
@@ -1258,34 +1325,34 @@
         <v>42.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
         <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1303,10 +1370,10 @@
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1318,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1339,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1348,16 +1415,16 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -1392,91 +1459,91 @@
         <v>62</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.806</v>
+        <v>0.79</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J6" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.393</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R6" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S6" t="n">
         <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U6" t="n">
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
@@ -1485,7 +1552,7 @@
         <v>17</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1497,7 +1564,7 @@
         <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1509,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
         <v>6</v>
@@ -1539,7 +1606,7 @@
         <v>21</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -1571,34 +1638,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.609</v>
+        <v>0.603</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N7" t="n">
         <v>0.347</v>
@@ -1610,10 +1677,10 @@
         <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S7" t="n">
         <v>31.6</v>
@@ -1622,7 +1689,7 @@
         <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
         <v>13.3</v>
@@ -1634,7 +1701,7 @@
         <v>5.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>19.3</v>
@@ -1643,16 +1710,16 @@
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.4</v>
+        <v>101.1</v>
       </c>
       <c r="AC7" t="n">
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1673,16 +1740,16 @@
         <v>9</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
       </c>
       <c r="AN7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO7" t="n">
         <v>23</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1712,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -1855,13 +1922,13 @@
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1879,13 +1946,13 @@
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2086,7 @@
         <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2031,7 +2098,7 @@
         <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2088,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF11" t="n">
         <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>6</v>
@@ -2392,7 +2459,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
         <v>20</v>
@@ -2431,7 +2498,7 @@
         <v>16</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
         <v>23.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
         <v>11.4</v>
@@ -2532,10 +2599,10 @@
         <v>43.6</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2544,10 +2611,10 @@
         <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" t="n">
         <v>21.3</v>
@@ -2556,16 +2623,16 @@
         <v>104.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>21</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2598,13 +2665,13 @@
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>2</v>
@@ -2613,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>19</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.234</v>
+        <v>0.238</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J13" t="n">
         <v>82</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
@@ -2693,22 +2760,22 @@
         <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R13" t="n">
         <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T13" t="n">
         <v>40.2</v>
@@ -2735,13 +2802,13 @@
         <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC13" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,25 +2820,25 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>29</v>
@@ -2786,7 +2853,7 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>21</v>
@@ -2798,7 +2865,7 @@
         <v>19</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,7 +2874,7 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.794</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P14" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>13.5</v>
@@ -2911,31 +2978,31 @@
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
         <v>22.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.7</v>
+        <v>108.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2950,19 +3017,19 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
@@ -2986,13 +3053,13 @@
         <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3235,7 @@
         <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3332,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>29</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -3409,61 +3476,61 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="O17" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V17" t="n">
         <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z17" t="n">
         <v>24.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
         <v>-0.4</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3484,13 +3551,13 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
@@ -3499,40 +3566,40 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="n">
         <v>13</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-5</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3669,7 +3736,7 @@
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3690,7 +3757,7 @@
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
@@ -3851,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3893,7 +3960,7 @@
         <v>18</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4088,7 @@
         <v>10</v>
       </c>
       <c r="AF20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
         <v>9</v>
@@ -4051,10 +4118,10 @@
         <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
         <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.413</v>
+        <v>0.403</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
@@ -4137,7 +4204,7 @@
         <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.446</v>
@@ -4146,25 +4213,25 @@
         <v>10.5</v>
       </c>
       <c r="M21" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.366</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="P21" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.795</v>
+        <v>0.792</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T21" t="n">
         <v>42.3</v>
@@ -4173,31 +4240,31 @@
         <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4230,16 +4297,16 @@
         <v>15</v>
       </c>
       <c r="AO21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP21" t="n">
         <v>23</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>22</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
         <v>8</v>
@@ -4254,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
         <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>0.281</v>
+        <v>0.27</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4322,7 +4389,7 @@
         <v>81.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
         <v>4.2</v>
@@ -4331,16 +4398,16 @@
         <v>11.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P22" t="n">
         <v>25.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.783</v>
+        <v>0.78</v>
       </c>
       <c r="R22" t="n">
         <v>12.4</v>
@@ -4352,13 +4419,13 @@
         <v>43.1</v>
       </c>
       <c r="U22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X22" t="n">
         <v>4.4</v>
@@ -4367,7 +4434,7 @@
         <v>4.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
         <v>20.8</v>
@@ -4376,13 +4443,13 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF22" t="n">
         <v>26</v>
@@ -4391,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="AH22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI22" t="n">
         <v>13</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>10</v>
@@ -4430,13 +4497,13 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4579,7 +4646,7 @@
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>10</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4618,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4828,7 @@
         <v>19</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK24" t="n">
         <v>16</v>
@@ -4806,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.531</v>
+        <v>0.54</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="J25" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.501</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
@@ -4880,13 +4947,13 @@
         <v>0.386</v>
       </c>
       <c r="O25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P25" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
         <v>10.2</v>
@@ -4895,10 +4962,10 @@
         <v>31.1</v>
       </c>
       <c r="T25" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V25" t="n">
         <v>16</v>
@@ -4919,37 +4986,37 @@
         <v>22.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.5</v>
+        <v>107.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
@@ -4958,13 +5025,13 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR25" t="n">
         <v>25</v>
@@ -4973,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" t="n">
         <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.645</v>
+        <v>0.635</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5092,25 +5159,25 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
         <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>6</v>
@@ -5119,13 +5186,13 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI26" t="n">
         <v>15</v>
       </c>
-      <c r="AI26" t="n">
-        <v>13</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5134,19 +5201,19 @@
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,22 +5234,22 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -5211,19 +5278,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="n">
         <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H27" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I27" t="n">
         <v>36.1</v>
@@ -5232,22 +5299,22 @@
         <v>80.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
         <v>6.8</v>
       </c>
       <c r="M27" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O27" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.801</v>
@@ -5265,7 +5332,7 @@
         <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
         <v>7</v>
@@ -5274,34 +5341,34 @@
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z27" t="n">
         <v>23.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB27" t="n">
         <v>99.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
       </c>
       <c r="AF27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,22 +5377,22 @@
         <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM27" t="n">
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
@@ -5334,7 +5401,7 @@
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>30</v>
@@ -5343,16 +5410,16 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY27" t="n">
         <v>20</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J28" t="n">
         <v>79.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M28" t="n">
         <v>20.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P28" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="n">
         <v>0.77</v>
@@ -5465,13 +5532,13 @@
         <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5516,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>18</v>
@@ -5534,7 +5601,7 @@
         <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5753,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="n">
         <v>28</v>
@@ -5707,7 +5774,7 @@
         <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5716,7 +5783,7 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5725,7 +5792,7 @@
         <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.641</v>
+        <v>0.635</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
@@ -5784,19 +5851,19 @@
         <v>4.8</v>
       </c>
       <c r="M30" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
         <v>28.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R30" t="n">
         <v>11.7</v>
@@ -5814,13 +5881,13 @@
         <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y30" t="n">
         <v>4.8</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
         <v>22.2</v>
@@ -5829,25 +5896,25 @@
         <v>23.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>7</v>
       </c>
       <c r="AF30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG30" t="n">
         <v>7</v>
       </c>
-      <c r="AG30" t="n">
-        <v>8</v>
-      </c>
       <c r="AH30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5889,16 +5956,16 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
@@ -6023,10 +6090,10 @@
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>29</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6074,7 +6141,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-10-2008-09</t>
+          <t>2009-03-10</t>
         </is>
       </c>
     </row>
